--- a/recon-tool/samples/ic_A.xlsx
+++ b/recon-tool/samples/ic_A.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -579,9 +579,69 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>4900000006</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>misc without ref</v>
+      </c>
+      <c r="D10" t="str">
+        <v>20/03/2026</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>4900000007</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>ho stray line</v>
+      </c>
+      <c r="D11" t="str">
+        <v>21/03/2026</v>
+      </c>
+      <c r="E11">
+        <v>15.5</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12">
+        <v>1005.5</v>
+      </c>
+      <c r="F12">
+        <v>1100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/recon-tool/samples/ic_A.xlsx
+++ b/recon-tool/samples/ic_A.xlsx
@@ -31,28 +31,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -61,13 +71,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -400,242 +412,242 @@
   <dimension ref="A1:F12"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Document Number</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="2" t="str">
         <v>Reference</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" s="2" t="str">
         <v>Text</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" s="2" t="str">
         <v>Document Date</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" s="2" t="str">
         <v>Debit Amount</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" s="2" t="str">
         <v>Credit Amount</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v>4900000001</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" s="2" t="str">
         <v>R-101</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="2" t="str">
         <v>HO invoice 1a</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" s="2" t="str">
         <v>10/01/2026</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v>4900000001</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="2" t="str">
         <v>R-101</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="2" t="str">
         <v>HO invoice 1b</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" s="2" t="str">
         <v>10/01/2026</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>50</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v>4900000001</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="2" t="str">
         <v>R-101</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="2" t="str">
         <v>HO invoice 1c</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" s="2" t="str">
         <v>10/01/2026</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>25</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v>4900000002</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="2" t="str">
         <v>R-102</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="2" t="str">
         <v>HO invoice 2</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="2" t="str">
         <v>05/02/2026</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>200</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v>4900000003</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B6" s="2" t="str">
         <v>R-103</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" s="2" t="str">
         <v>HO invoice 3</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" s="2" t="str">
         <v>12/02/2026</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>500</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v>4900000003</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="2" t="str">
         <v>R-103</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C7" s="2" t="str">
         <v>HO credit note</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" s="2" t="str">
         <v>13/02/2026</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v>4900000004</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B8" s="2" t="str">
         <v>T-9</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" s="2" t="str">
         <v>transfer to lim</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D8" s="2" t="str">
         <v>01/03/2026</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v>4900000005</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B9" s="2" t="str">
         <v>H-77</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9" s="2" t="str">
         <v>ho only item</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D9" s="2" t="str">
         <v>15/03/2026</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>75</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v>4900000006</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B10" s="2" t="str">
         <v/>
       </c>
-      <c r="C10" t="str">
+      <c r="C10" s="2" t="str">
         <v>misc without ref</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="2" t="str">
         <v>20/03/2026</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>40</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v>4900000007</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11" s="2" t="str">
         <v/>
       </c>
-      <c r="C11" t="str">
+      <c r="C11" s="2" t="str">
         <v>ho stray line</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" s="2" t="str">
         <v>21/03/2026</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>15.5</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v/>
       </c>
-      <c r="B12" t="str">
+      <c r="B12" s="2" t="str">
         <v/>
       </c>
-      <c r="C12" t="str">
+      <c r="C12" s="2" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="2" t="str">
         <v/>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>1005.5</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>1100</v>
       </c>
     </row>
